--- a/data/RETAILER data Deatils.xlsx
+++ b/data/RETAILER data Deatils.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PRANAVI\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D60184B-A396-4420-9372-64FD4F2279BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34611D4B-426E-4B84-A2E5-1D2617C2E4D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2874" uniqueCount="1833">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3368" uniqueCount="2007">
   <si>
     <t>DB Name</t>
   </si>
@@ -5522,6 +5522,528 @@
   </si>
   <si>
     <t>DOMJUR</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> L P MOTOR PARTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> RADIANT MOTORS</t>
+  </si>
+  <si>
+    <t>A K ENTERPRISE</t>
+  </si>
+  <si>
+    <t>A V DESIGNO</t>
+  </si>
+  <si>
+    <t>AARIN SWITCHGEAR CORNER</t>
+  </si>
+  <si>
+    <t>AAYANA ENTERPRISE</t>
+  </si>
+  <si>
+    <t>ADMINISTRATIVE OFFICER,KOLKATA POOL CAR</t>
+  </si>
+  <si>
+    <t>ADYAMA METAL BOX</t>
+  </si>
+  <si>
+    <t>Affortable Tech Services Private Limited</t>
+  </si>
+  <si>
+    <t>AIRPORT AUTHORITY OF INDIA (N.A.D.)</t>
+  </si>
+  <si>
+    <t>ALFA SOLUTIONS</t>
+  </si>
+  <si>
+    <t>AMBIKA MOTOR &amp; SONS</t>
+  </si>
+  <si>
+    <t>ANAND AUTO SYNDICATE</t>
+  </si>
+  <si>
+    <t>ANGEL TRANSPORT AND HANDLING SERVICES LL</t>
+  </si>
+  <si>
+    <t>ANNAPURNA MOTOR PARTS</t>
+  </si>
+  <si>
+    <t>Aparajita Automobile</t>
+  </si>
+  <si>
+    <t>APEX INTERNATIONAL</t>
+  </si>
+  <si>
+    <t>ASIS KUMAR BASU</t>
+  </si>
+  <si>
+    <t>ASOK COMMERCIAL</t>
+  </si>
+  <si>
+    <t>AUTO ACCESSORIES &amp; Co.</t>
+  </si>
+  <si>
+    <t>AUTO CARE</t>
+  </si>
+  <si>
+    <t>AUTO MEDIK</t>
+  </si>
+  <si>
+    <t>AYUSH EARTMOVERS</t>
+  </si>
+  <si>
+    <t>AZAD AUTOMOBILE</t>
+  </si>
+  <si>
+    <t>B D MOTORS</t>
+  </si>
+  <si>
+    <t>B M AUTO PARTS</t>
+  </si>
+  <si>
+    <t>B.S . MOTORS</t>
+  </si>
+  <si>
+    <t>BABA RAMDEV AUTOMOBILES</t>
+  </si>
+  <si>
+    <t>Balaji Auto Centre</t>
+  </si>
+  <si>
+    <t>BARUI AUTO MOBILE</t>
+  </si>
+  <si>
+    <t>BELA TRANSPORT &amp; SUPPLIERS</t>
+  </si>
+  <si>
+    <t>BENGAL MARINE AGENCY</t>
+  </si>
+  <si>
+    <t>BHAGYA ENTERPRISE</t>
+  </si>
+  <si>
+    <t>BIDYUT SHILPA LTD.</t>
+  </si>
+  <si>
+    <t>BIPLAB MOTOR PARTS</t>
+  </si>
+  <si>
+    <t>BISWAKARMA MOTOR GARAGE</t>
+  </si>
+  <si>
+    <t>Blue Star Auto Works</t>
+  </si>
+  <si>
+    <t>BLUE WINGS</t>
+  </si>
+  <si>
+    <t>BM ENTERPRISES</t>
+  </si>
+  <si>
+    <t>BRITE POLYTECH PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>CLASSIC  ENTERPRISES( MANIK TALA)</t>
+  </si>
+  <si>
+    <t>DAS MOTORS</t>
+  </si>
+  <si>
+    <t>DEBASIS MITRA</t>
+  </si>
+  <si>
+    <t>DELUX MOTOR</t>
+  </si>
+  <si>
+    <t>DHAN LAMINATES PVT. LTD.</t>
+  </si>
+  <si>
+    <t>EVERGREEN ENTERPRISE</t>
+  </si>
+  <si>
+    <t>EXPRESS TRADING AGENCIES</t>
+  </si>
+  <si>
+    <t>GARDEN REACH ASBESTOS AGENCY</t>
+  </si>
+  <si>
+    <t>GARGI TRAVELS PVT LTD</t>
+  </si>
+  <si>
+    <t>GEETA MOTOR</t>
+  </si>
+  <si>
+    <t>GERMAN APEX MULTI BRAND PREMIUM CAR WORK</t>
+  </si>
+  <si>
+    <t>GLOWRY Automobile  (P)Ltd</t>
+  </si>
+  <si>
+    <t>GRAND MOTORS</t>
+  </si>
+  <si>
+    <t>H B ENTERPRISE</t>
+  </si>
+  <si>
+    <t>Hazi Motor</t>
+  </si>
+  <si>
+    <t>HAZRA ENTERPRISE</t>
+  </si>
+  <si>
+    <t>HYTECH INDIA EARTHMOVERS</t>
+  </si>
+  <si>
+    <t>INDIAN AUTO SUPPLY CORPORATION</t>
+  </si>
+  <si>
+    <t>INTERNATIONAL  SPARE CORPORATION</t>
+  </si>
+  <si>
+    <t>International Automobiles</t>
+  </si>
+  <si>
+    <t>J. P. CREATION</t>
+  </si>
+  <si>
+    <t>J.B TRADERS</t>
+  </si>
+  <si>
+    <t>JOY AUTOMOBILES</t>
+  </si>
+  <si>
+    <t>JOYDEEP ENTERPRISE</t>
+  </si>
+  <si>
+    <t>K S MOTORS</t>
+  </si>
+  <si>
+    <t>K.S EARTHMOVERS</t>
+  </si>
+  <si>
+    <t>K.S. SALES</t>
+  </si>
+  <si>
+    <t>KARUNAMOYEE MOTORS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>KING SHOES</t>
+  </si>
+  <si>
+    <t>Kiran Automobiles</t>
+  </si>
+  <si>
+    <t>KPT MOTORS</t>
+  </si>
+  <si>
+    <t>KRISHNA AUTOMOBILES</t>
+  </si>
+  <si>
+    <t>KRISHNA CHANDRA PLASTIC CORPORATION</t>
+  </si>
+  <si>
+    <t>KRISHNA GHOSH</t>
+  </si>
+  <si>
+    <t>LAKHMI MOTOR STORES &amp; CO</t>
+  </si>
+  <si>
+    <t>LANSDOWNE AUTOMOBILE</t>
+  </si>
+  <si>
+    <t>LBG AUTOMOBILES</t>
+  </si>
+  <si>
+    <t>Lexicon Commercial Enterprises Limited</t>
+  </si>
+  <si>
+    <t>M.M.K PROCESS</t>
+  </si>
+  <si>
+    <t>M/S  UTKARSH INDIA LTD</t>
+  </si>
+  <si>
+    <t>M/S CHOUDHURY AUTOMOBILE</t>
+  </si>
+  <si>
+    <t>M/S GUPTA CEMENT AGENCY</t>
+  </si>
+  <si>
+    <t>M/S LAXMI NARAYAN AUTOMOBILES</t>
+  </si>
+  <si>
+    <t>M/S MAJI TYRES</t>
+  </si>
+  <si>
+    <t>M/S MALLICK ENTERPRISE</t>
+  </si>
+  <si>
+    <t>M/S. MOHD. SHAHNAWAZ KHAN</t>
+  </si>
+  <si>
+    <t>M/S. PIJUS KANTI SAHA</t>
+  </si>
+  <si>
+    <t>MAA BHABANI AUTO SPARES</t>
+  </si>
+  <si>
+    <t>MAA PADMAVATI TRADING CO.</t>
+  </si>
+  <si>
+    <t>MAA SHAILPUTRI LOGISTICS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>MACHGUARD ENTERPRISES</t>
+  </si>
+  <si>
+    <t>MADHUMITA HANDICRAFTS</t>
+  </si>
+  <si>
+    <t>MAHAVEER AUTOMOBILES</t>
+  </si>
+  <si>
+    <t>MAHESH CAR REPAIRING CENTRE</t>
+  </si>
+  <si>
+    <t>MAJI ENTERPRISE</t>
+  </si>
+  <si>
+    <t>MAJUMDER AUTOMOBILE</t>
+  </si>
+  <si>
+    <t>MALKIT SINGH</t>
+  </si>
+  <si>
+    <t>MAMATA ENTERPRISE</t>
+  </si>
+  <si>
+    <t>MANOJ AUTO CENTRE</t>
+  </si>
+  <si>
+    <t>MARKOPOLO INDUSTRIAL CORPORATION</t>
+  </si>
+  <si>
+    <t>MAYA AUTOMOBILE (BARACKPORE)</t>
+  </si>
+  <si>
+    <t>MEHTAB AUTO SALES</t>
+  </si>
+  <si>
+    <t>METROPOLITAN TRANSPORT CO</t>
+  </si>
+  <si>
+    <t>MILAN ENTERPRISE</t>
+  </si>
+  <si>
+    <t>MONALISA NURSING CENTRE</t>
+  </si>
+  <si>
+    <t>MONDAL BRICK FIELD, KRISHNA KALI BRICK F</t>
+  </si>
+  <si>
+    <t>MUKESH AOTUMOBILE ELECTRONICS</t>
+  </si>
+  <si>
+    <t>N. R. CONSTRUCTION &amp; NURSERY</t>
+  </si>
+  <si>
+    <t>NATRAJ LUBRICATING HOUSE</t>
+  </si>
+  <si>
+    <t>NEED TECH PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>NEON ENTERPRISE</t>
+  </si>
+  <si>
+    <t>NEW BARGHABIMA AUTO PARTS</t>
+  </si>
+  <si>
+    <t>NEW BENGAL AUTOMOTIV</t>
+  </si>
+  <si>
+    <t>NEW PALKI CAR DECORA</t>
+  </si>
+  <si>
+    <t>NEW SUKANTA AGENCY (INDIA)</t>
+  </si>
+  <si>
+    <t>PAL EQUIPMENTS</t>
+  </si>
+  <si>
+    <t>PAL SPARE</t>
+  </si>
+  <si>
+    <t>PANACHE SOLUTIONS</t>
+  </si>
+  <si>
+    <t>PANNA AUTOMOBILES</t>
+  </si>
+  <si>
+    <t>Pearl Automobiles</t>
+  </si>
+  <si>
+    <t>PLATTER HOSPITALITY PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>PRABHOJI MOTORS</t>
+  </si>
+  <si>
+    <t>PRADEEP MOTOR (TOPSIA)</t>
+  </si>
+  <si>
+    <t>PREDATOR COMMODITIES PVT LTD</t>
+  </si>
+  <si>
+    <t>PRIME MOTORS</t>
+  </si>
+  <si>
+    <t>RAM AUTOMOBILE</t>
+  </si>
+  <si>
+    <t>REFTECH CONTAINER SERVICES PVT LTD</t>
+  </si>
+  <si>
+    <t>Royal Auto Emporium</t>
+  </si>
+  <si>
+    <t>S &amp; S ENTERPRISE( Garden  Reach)</t>
+  </si>
+  <si>
+    <t>S.K. TURBO EQUIPMENTS</t>
+  </si>
+  <si>
+    <t>S.MOTOR WORKS</t>
+  </si>
+  <si>
+    <t>S.R TRADING CO.</t>
+  </si>
+  <si>
+    <t>S.S. MOTOR PARTS &amp; ACCESSORIES</t>
+  </si>
+  <si>
+    <t>SAMPARK ADVERTISING &amp; MEDIA PVT.LTD</t>
+  </si>
+  <si>
+    <t>SAYANIKA MOTOR PARTS SALES AND SERVICE</t>
+  </si>
+  <si>
+    <t>SHAILENDRA KUMAR SHARMA</t>
+  </si>
+  <si>
+    <t>SHAW BROTHERS</t>
+  </si>
+  <si>
+    <t>SHEETLA CASTING PVT.LTD</t>
+  </si>
+  <si>
+    <t>SHREE BALAJI TRADERS</t>
+  </si>
+  <si>
+    <t>SHYAM AUTO MART</t>
+  </si>
+  <si>
+    <t>Shyama Motors</t>
+  </si>
+  <si>
+    <t>SIKHA AUTO PARTS</t>
+  </si>
+  <si>
+    <t>SIT Auto Parts</t>
+  </si>
+  <si>
+    <t>South Auto Centre</t>
+  </si>
+  <si>
+    <t>SREEMA DYEING &amp; BLEACHING WORKS</t>
+  </si>
+  <si>
+    <t>SRI KRISHNA AUTOMOBILES</t>
+  </si>
+  <si>
+    <t>SRI RAM MOTORS (ARAMBAGH)</t>
+  </si>
+  <si>
+    <t>STAR ENTERPRISE</t>
+  </si>
+  <si>
+    <t>SUBHA UDYOG</t>
+  </si>
+  <si>
+    <t>SUCHITA MILLENIUM PROJECTS PVT LTD</t>
+  </si>
+  <si>
+    <t>SUDIPA DUTTA</t>
+  </si>
+  <si>
+    <t>Sushila Automobile</t>
+  </si>
+  <si>
+    <t>SUVRAJIT BHATTACHARYA</t>
+  </si>
+  <si>
+    <t>SWARNALATA AUTO SERVICE CENTRE</t>
+  </si>
+  <si>
+    <t>SWASTIK TRADELINK</t>
+  </si>
+  <si>
+    <t>T.A ROADLINES</t>
+  </si>
+  <si>
+    <t>T.R. MOTORS</t>
+  </si>
+  <si>
+    <t>TACLIM SEKH</t>
+  </si>
+  <si>
+    <t>TECH-MECH</t>
+  </si>
+  <si>
+    <t>TEJAS SUPPLY CHAIN PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>THE LAM HUB</t>
+  </si>
+  <si>
+    <t>THE MOTOR CADE</t>
+  </si>
+  <si>
+    <t>THE SOUTH MOTOR STORES</t>
+  </si>
+  <si>
+    <t>TVS AUTOMOBILE SOLUTIONS PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>V.D.Kakad &amp; Co.</t>
+  </si>
+  <si>
+    <t>VEDANT SERVICE PRIVATE LIMITED</t>
+  </si>
+  <si>
+    <t>VOLGO  SPARES</t>
+  </si>
+  <si>
+    <t>9038899962</t>
+  </si>
+  <si>
+    <t>HOWRAH</t>
+  </si>
+  <si>
+    <t>SOUTH 24 PARGANAS</t>
+  </si>
+  <si>
+    <t>Paschim Medinipur</t>
+  </si>
+  <si>
+    <t>Hugli</t>
+  </si>
+  <si>
+    <t>North Twenty Four Parganas</t>
+  </si>
+  <si>
+    <t>South Twenty Four Parganas</t>
   </si>
 </sst>
 </file>
@@ -5543,7 +6065,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5556,8 +6078,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -5580,15 +6108,63 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5931,11 +6507,11 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:K284"/>
+  <dimension ref="A1:K451"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.19921875" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="10.796875" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="22.796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.59765625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46.796875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.19921875" bestFit="1" customWidth="1"/>
@@ -15387,6 +15963,1843 @@
         <v>1828</v>
       </c>
     </row>
+    <row r="285" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C285" s="6" t="s">
+        <v>1833</v>
+      </c>
+      <c r="H285" s="4" t="s">
+        <v>2001</v>
+      </c>
+      <c r="I285" s="8">
+        <v>9875363128</v>
+      </c>
+    </row>
+    <row r="286" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C286" s="7" t="s">
+        <v>1834</v>
+      </c>
+      <c r="H286" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I286" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="287" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C287" s="6" t="s">
+        <v>1835</v>
+      </c>
+      <c r="H287" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I287" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="288" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="C288" s="7" t="s">
+        <v>1836</v>
+      </c>
+      <c r="H288" s="5" t="s">
+        <v>2002</v>
+      </c>
+      <c r="I288" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="289" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C289" s="6" t="s">
+        <v>1837</v>
+      </c>
+      <c r="H289" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I289" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="290" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C290" s="7" t="s">
+        <v>1838</v>
+      </c>
+      <c r="H290" s="5" t="s">
+        <v>2002</v>
+      </c>
+      <c r="I290" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="291" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C291" s="6" t="s">
+        <v>1839</v>
+      </c>
+      <c r="H291" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I291" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="292" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C292" s="7" t="s">
+        <v>1840</v>
+      </c>
+      <c r="H292" s="5" t="s">
+        <v>2002</v>
+      </c>
+      <c r="I292" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="293" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C293" s="6" t="s">
+        <v>1841</v>
+      </c>
+      <c r="H293" s="4" t="s">
+        <v>2003</v>
+      </c>
+      <c r="I293" s="6">
+        <v>7044032905</v>
+      </c>
+    </row>
+    <row r="294" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C294" s="7" t="s">
+        <v>1842</v>
+      </c>
+      <c r="H294" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I294" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="295" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C295" s="6" t="s">
+        <v>1843</v>
+      </c>
+      <c r="H295" s="4" t="s">
+        <v>2003</v>
+      </c>
+      <c r="I295" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="296" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C296" s="7" t="s">
+        <v>1844</v>
+      </c>
+      <c r="H296" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I296" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="297" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C297" s="6" t="s">
+        <v>1845</v>
+      </c>
+      <c r="H297" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I297" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="298" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C298" s="7" t="s">
+        <v>1846</v>
+      </c>
+      <c r="H298" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I298" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="299" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C299" s="6" t="s">
+        <v>1847</v>
+      </c>
+      <c r="H299" s="4" t="s">
+        <v>2003</v>
+      </c>
+      <c r="I299" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="300" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C300" s="7" t="s">
+        <v>1848</v>
+      </c>
+      <c r="H300" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="I300" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="301" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C301" s="6" t="s">
+        <v>1849</v>
+      </c>
+      <c r="H301" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I301" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="302" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C302" s="7" t="s">
+        <v>1850</v>
+      </c>
+      <c r="H302" s="5" t="s">
+        <v>2001</v>
+      </c>
+      <c r="I302" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="303" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C303" s="6" t="s">
+        <v>1851</v>
+      </c>
+      <c r="H303" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I303" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="304" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C304" s="7" t="s">
+        <v>1852</v>
+      </c>
+      <c r="H304" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I304" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="305" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C305" s="6" t="s">
+        <v>1853</v>
+      </c>
+      <c r="H305" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="I305" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="306" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C306" s="7" t="s">
+        <v>1854</v>
+      </c>
+      <c r="H306" s="5" t="s">
+        <v>2003</v>
+      </c>
+      <c r="I306" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="307" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C307" s="6" t="s">
+        <v>1855</v>
+      </c>
+      <c r="H307" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I307" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="308" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C308" s="7" t="s">
+        <v>1856</v>
+      </c>
+      <c r="H308" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I308" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="309" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C309" s="6" t="s">
+        <v>1857</v>
+      </c>
+      <c r="H309" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I309" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="310" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C310" s="7" t="s">
+        <v>1858</v>
+      </c>
+      <c r="H310" s="5" t="s">
+        <v>2001</v>
+      </c>
+      <c r="I310" s="7">
+        <v>9830239693</v>
+      </c>
+    </row>
+    <row r="311" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C311" s="6" t="s">
+        <v>1859</v>
+      </c>
+      <c r="H311" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="I311" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="312" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C312" s="7" t="s">
+        <v>1860</v>
+      </c>
+      <c r="H312" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I312" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="313" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C313" s="6" t="s">
+        <v>1861</v>
+      </c>
+      <c r="H313" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I313" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="314" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C314" s="7" t="s">
+        <v>1862</v>
+      </c>
+      <c r="H314" s="5" t="s">
+        <v>2001</v>
+      </c>
+      <c r="I314" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="315" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C315" s="6" t="s">
+        <v>1863</v>
+      </c>
+      <c r="H315" s="4" t="s">
+        <v>2002</v>
+      </c>
+      <c r="I315" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="316" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C316" s="7" t="s">
+        <v>1864</v>
+      </c>
+      <c r="H316" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I316" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="317" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C317" s="6" t="s">
+        <v>1865</v>
+      </c>
+      <c r="H317" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I317" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="318" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C318" s="7" t="s">
+        <v>1866</v>
+      </c>
+      <c r="H318" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I318" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="319" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C319" s="6" t="s">
+        <v>1867</v>
+      </c>
+      <c r="H319" s="4" t="s">
+        <v>2003</v>
+      </c>
+      <c r="I319" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="320" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C320" s="7" t="s">
+        <v>1868</v>
+      </c>
+      <c r="H320" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I320" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="321" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C321" s="6" t="s">
+        <v>1869</v>
+      </c>
+      <c r="H321" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I321" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="322" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C322" s="7" t="s">
+        <v>1870</v>
+      </c>
+      <c r="H322" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I322" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="323" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C323" s="6" t="s">
+        <v>1871</v>
+      </c>
+      <c r="H323" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I323" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="324" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C324" s="7" t="s">
+        <v>1872</v>
+      </c>
+      <c r="H324" s="5" t="s">
+        <v>2001</v>
+      </c>
+      <c r="I324" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="325" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C325" s="6" t="s">
+        <v>1873</v>
+      </c>
+      <c r="H325" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I325" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="326" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C326" s="7" t="s">
+        <v>1874</v>
+      </c>
+      <c r="H326" s="5" t="s">
+        <v>2004</v>
+      </c>
+      <c r="I326" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="327" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C327" s="6" t="s">
+        <v>1875</v>
+      </c>
+      <c r="H327" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I327" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="328" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C328" s="7" t="s">
+        <v>1876</v>
+      </c>
+      <c r="H328" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="I328" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="329" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C329" s="6" t="s">
+        <v>1877</v>
+      </c>
+      <c r="H329" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I329" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="330" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C330" s="7" t="s">
+        <v>1878</v>
+      </c>
+      <c r="H330" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I330" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="331" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C331" s="6" t="s">
+        <v>1879</v>
+      </c>
+      <c r="H331" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I331" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="332" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C332" s="7" t="s">
+        <v>1880</v>
+      </c>
+      <c r="H332" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I332" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="333" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C333" s="6" t="s">
+        <v>1881</v>
+      </c>
+      <c r="H333" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I333" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="334" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C334" s="7" t="s">
+        <v>1882</v>
+      </c>
+      <c r="H334" s="5" t="s">
+        <v>2004</v>
+      </c>
+      <c r="I334" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="335" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C335" s="6" t="s">
+        <v>1883</v>
+      </c>
+      <c r="H335" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I335" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="336" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C336" s="7" t="s">
+        <v>1884</v>
+      </c>
+      <c r="H336" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I336" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="337" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C337" s="6" t="s">
+        <v>1885</v>
+      </c>
+      <c r="H337" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="I337" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="338" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C338" s="7" t="s">
+        <v>1886</v>
+      </c>
+      <c r="H338" s="5" t="s">
+        <v>2002</v>
+      </c>
+      <c r="I338" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="339" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C339" s="6" t="s">
+        <v>1887</v>
+      </c>
+      <c r="H339" s="4" t="s">
+        <v>2003</v>
+      </c>
+      <c r="I339" s="6">
+        <v>9932596911</v>
+      </c>
+    </row>
+    <row r="340" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C340" s="7" t="s">
+        <v>1888</v>
+      </c>
+      <c r="H340" s="5" t="s">
+        <v>2002</v>
+      </c>
+      <c r="I340" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="341" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C341" s="6" t="s">
+        <v>1889</v>
+      </c>
+      <c r="H341" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I341" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="342" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C342" s="7" t="s">
+        <v>1890</v>
+      </c>
+      <c r="H342" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I342" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="343" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C343" s="6" t="s">
+        <v>1891</v>
+      </c>
+      <c r="H343" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I343" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="344" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C344" s="7" t="s">
+        <v>1892</v>
+      </c>
+      <c r="H344" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I344" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="345" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C345" s="6" t="s">
+        <v>1893</v>
+      </c>
+      <c r="H345" s="4" t="s">
+        <v>2002</v>
+      </c>
+      <c r="I345" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="346" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C346" s="7" t="s">
+        <v>1894</v>
+      </c>
+      <c r="H346" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="I346" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="347" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C347" s="6" t="s">
+        <v>1895</v>
+      </c>
+      <c r="H347" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I347" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="348" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C348" s="7" t="s">
+        <v>1896</v>
+      </c>
+      <c r="H348" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I348" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="349" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C349" s="6" t="s">
+        <v>1897</v>
+      </c>
+      <c r="H349" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="I349" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="350" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C350" s="7" t="s">
+        <v>1898</v>
+      </c>
+      <c r="H350" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I350" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="351" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C351" s="6" t="s">
+        <v>1899</v>
+      </c>
+      <c r="H351" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I351" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="352" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C352" s="7" t="s">
+        <v>1900</v>
+      </c>
+      <c r="H352" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I352" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="353" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C353" s="6" t="s">
+        <v>1901</v>
+      </c>
+      <c r="H353" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I353" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="354" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C354" s="7" t="s">
+        <v>1902</v>
+      </c>
+      <c r="H354" s="5" t="s">
+        <v>2003</v>
+      </c>
+      <c r="I354" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="355" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C355" s="6" t="s">
+        <v>1903</v>
+      </c>
+      <c r="H355" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I355" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="356" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C356" s="7" t="s">
+        <v>1904</v>
+      </c>
+      <c r="H356" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="I356" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="357" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C357" s="6" t="s">
+        <v>1905</v>
+      </c>
+      <c r="H357" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I357" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="358" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C358" s="7" t="s">
+        <v>1906</v>
+      </c>
+      <c r="H358" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="I358" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="359" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C359" s="6" t="s">
+        <v>1907</v>
+      </c>
+      <c r="H359" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I359" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="360" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C360" s="7" t="s">
+        <v>1908</v>
+      </c>
+      <c r="H360" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I360" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="361" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C361" s="6" t="s">
+        <v>1909</v>
+      </c>
+      <c r="H361" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="I361" s="6">
+        <v>9933478238</v>
+      </c>
+    </row>
+    <row r="362" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C362" s="7" t="s">
+        <v>1910</v>
+      </c>
+      <c r="H362" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I362" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="363" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C363" s="6" t="s">
+        <v>1911</v>
+      </c>
+      <c r="H363" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I363" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="364" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C364" s="7" t="s">
+        <v>1912</v>
+      </c>
+      <c r="H364" s="5" t="s">
+        <v>2001</v>
+      </c>
+      <c r="I364" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="365" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C365" s="6" t="s">
+        <v>1913</v>
+      </c>
+      <c r="H365" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I365" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="366" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C366" s="7" t="s">
+        <v>1914</v>
+      </c>
+      <c r="H366" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I366" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="367" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C367" s="6" t="s">
+        <v>1915</v>
+      </c>
+      <c r="H367" s="4" t="s">
+        <v>2003</v>
+      </c>
+      <c r="I367" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="368" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C368" s="7" t="s">
+        <v>1916</v>
+      </c>
+      <c r="H368" s="5" t="s">
+        <v>2003</v>
+      </c>
+      <c r="I368" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="369" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C369" s="6" t="s">
+        <v>1917</v>
+      </c>
+      <c r="H369" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I369" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="370" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C370" s="7" t="s">
+        <v>1918</v>
+      </c>
+      <c r="H370" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I370" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="371" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C371" s="6" t="s">
+        <v>1919</v>
+      </c>
+      <c r="H371" s="4" t="s">
+        <v>2005</v>
+      </c>
+      <c r="I371" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="372" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C372" s="7" t="s">
+        <v>1920</v>
+      </c>
+      <c r="H372" s="5" t="s">
+        <v>2003</v>
+      </c>
+      <c r="I372" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="373" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C373" s="6" t="s">
+        <v>1921</v>
+      </c>
+      <c r="H373" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I373" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="374" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C374" s="7" t="s">
+        <v>1922</v>
+      </c>
+      <c r="H374" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I374" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="375" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C375" s="6" t="s">
+        <v>1923</v>
+      </c>
+      <c r="H375" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I375" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="376" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C376" s="7" t="s">
+        <v>1924</v>
+      </c>
+      <c r="H376" s="5" t="s">
+        <v>2002</v>
+      </c>
+      <c r="I376" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="377" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C377" s="6" t="s">
+        <v>1925</v>
+      </c>
+      <c r="H377" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I377" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="378" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C378" s="7" t="s">
+        <v>1926</v>
+      </c>
+      <c r="H378" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I378" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="379" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C379" s="6" t="s">
+        <v>1927</v>
+      </c>
+      <c r="H379" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="I379" s="6">
+        <v>7029251129</v>
+      </c>
+    </row>
+    <row r="380" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C380" s="7" t="s">
+        <v>1928</v>
+      </c>
+      <c r="H380" s="5" t="s">
+        <v>2005</v>
+      </c>
+      <c r="I380" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="381" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C381" s="6" t="s">
+        <v>1929</v>
+      </c>
+      <c r="H381" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I381" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="382" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C382" s="7" t="s">
+        <v>1930</v>
+      </c>
+      <c r="H382" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I382" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="383" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C383" s="6" t="s">
+        <v>1931</v>
+      </c>
+      <c r="H383" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I383" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="384" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C384" s="7" t="s">
+        <v>1932</v>
+      </c>
+      <c r="H384" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I384" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="385" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C385" s="6" t="s">
+        <v>1933</v>
+      </c>
+      <c r="H385" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I385" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="386" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C386" s="7" t="s">
+        <v>1934</v>
+      </c>
+      <c r="H386" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I386" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="387" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C387" s="6" t="s">
+        <v>1935</v>
+      </c>
+      <c r="H387" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I387" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="388" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C388" s="7" t="s">
+        <v>1936</v>
+      </c>
+      <c r="H388" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I388" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="389" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C389" s="6" t="s">
+        <v>1937</v>
+      </c>
+      <c r="H389" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I389" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="390" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C390" s="7" t="s">
+        <v>1938</v>
+      </c>
+      <c r="H390" s="5" t="s">
+        <v>2002</v>
+      </c>
+      <c r="I390" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="391" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C391" s="6" t="s">
+        <v>1939</v>
+      </c>
+      <c r="H391" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I391" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="392" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C392" s="7" t="s">
+        <v>1940</v>
+      </c>
+      <c r="H392" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="I392" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="393" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C393" s="6" t="s">
+        <v>1941</v>
+      </c>
+      <c r="H393" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="I393" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="394" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C394" s="7" t="s">
+        <v>1942</v>
+      </c>
+      <c r="H394" s="5" t="s">
+        <v>2001</v>
+      </c>
+      <c r="I394" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="395" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C395" s="6" t="s">
+        <v>1943</v>
+      </c>
+      <c r="H395" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I395" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="396" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C396" s="7" t="s">
+        <v>1944</v>
+      </c>
+      <c r="H396" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="I396" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="397" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C397" s="6" t="s">
+        <v>1945</v>
+      </c>
+      <c r="H397" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="I397" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="398" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C398" s="7" t="s">
+        <v>1946</v>
+      </c>
+      <c r="H398" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I398" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="399" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C399" s="6" t="s">
+        <v>1947</v>
+      </c>
+      <c r="H399" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I399" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="400" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C400" s="7" t="s">
+        <v>1948</v>
+      </c>
+      <c r="H400" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I400" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="401" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C401" s="6" t="s">
+        <v>1949</v>
+      </c>
+      <c r="H401" s="4" t="s">
+        <v>2003</v>
+      </c>
+      <c r="I401" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="402" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C402" s="7" t="s">
+        <v>1950</v>
+      </c>
+      <c r="H402" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I402" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="403" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C403" s="6" t="s">
+        <v>1951</v>
+      </c>
+      <c r="H403" s="4" t="s">
+        <v>2003</v>
+      </c>
+      <c r="I403" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="404" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C404" s="7" t="s">
+        <v>1952</v>
+      </c>
+      <c r="H404" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I404" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="405" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C405" s="6" t="s">
+        <v>1953</v>
+      </c>
+      <c r="H405" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I405" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="406" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C406" s="7" t="s">
+        <v>1954</v>
+      </c>
+      <c r="H406" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I406" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="407" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C407" s="6" t="s">
+        <v>1955</v>
+      </c>
+      <c r="H407" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I407" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="408" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C408" s="7" t="s">
+        <v>1956</v>
+      </c>
+      <c r="H408" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I408" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="409" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C409" s="6" t="s">
+        <v>1957</v>
+      </c>
+      <c r="H409" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I409" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="410" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C410" s="7" t="s">
+        <v>1958</v>
+      </c>
+      <c r="H410" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="I410" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="411" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C411" s="6" t="s">
+        <v>1959</v>
+      </c>
+      <c r="H411" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I411" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="412" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C412" s="7" t="s">
+        <v>1960</v>
+      </c>
+      <c r="H412" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I412" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="413" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C413" s="6" t="s">
+        <v>1961</v>
+      </c>
+      <c r="H413" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I413" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="414" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C414" s="7" t="s">
+        <v>1962</v>
+      </c>
+      <c r="H414" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I414" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="415" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C415" s="6" t="s">
+        <v>1963</v>
+      </c>
+      <c r="H415" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I415" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="416" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C416" s="7" t="s">
+        <v>1964</v>
+      </c>
+      <c r="H416" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I416" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="417" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C417" s="6" t="s">
+        <v>1965</v>
+      </c>
+      <c r="H417" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I417" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="418" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C418" s="7" t="s">
+        <v>1966</v>
+      </c>
+      <c r="H418" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I418" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="419" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C419" s="6" t="s">
+        <v>1967</v>
+      </c>
+      <c r="H419" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I419" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="420" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C420" s="7" t="s">
+        <v>1968</v>
+      </c>
+      <c r="H420" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I420" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="421" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C421" s="6" t="s">
+        <v>1969</v>
+      </c>
+      <c r="H421" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="I421" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="422" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C422" s="7" t="s">
+        <v>1970</v>
+      </c>
+      <c r="H422" s="5" t="s">
+        <v>2001</v>
+      </c>
+      <c r="I422" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="423" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C423" s="6" t="s">
+        <v>1971</v>
+      </c>
+      <c r="H423" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I423" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="424" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C424" s="7" t="s">
+        <v>1972</v>
+      </c>
+      <c r="H424" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="I424" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="425" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C425" s="6" t="s">
+        <v>1973</v>
+      </c>
+      <c r="H425" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I425" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="426" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C426" s="7" t="s">
+        <v>1974</v>
+      </c>
+      <c r="H426" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="I426" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="427" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C427" s="6" t="s">
+        <v>1975</v>
+      </c>
+      <c r="H427" s="4" t="s">
+        <v>2006</v>
+      </c>
+      <c r="I427" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="428" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C428" s="7" t="s">
+        <v>1976</v>
+      </c>
+      <c r="H428" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I428" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="429" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C429" s="6" t="s">
+        <v>1977</v>
+      </c>
+      <c r="H429" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I429" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="430" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C430" s="7" t="s">
+        <v>1978</v>
+      </c>
+      <c r="H430" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="I430" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="431" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C431" s="6" t="s">
+        <v>1979</v>
+      </c>
+      <c r="H431" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="I431" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="432" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C432" s="7" t="s">
+        <v>1980</v>
+      </c>
+      <c r="H432" s="5" t="s">
+        <v>2005</v>
+      </c>
+      <c r="I432" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="433" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C433" s="6" t="s">
+        <v>1981</v>
+      </c>
+      <c r="H433" s="4" t="s">
+        <v>2002</v>
+      </c>
+      <c r="I433" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="434" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C434" s="7" t="s">
+        <v>1982</v>
+      </c>
+      <c r="H434" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I434" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="435" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C435" s="6" t="s">
+        <v>1983</v>
+      </c>
+      <c r="H435" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I435" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="436" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C436" s="7" t="s">
+        <v>1984</v>
+      </c>
+      <c r="H436" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="I436" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="437" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C437" s="6" t="s">
+        <v>1985</v>
+      </c>
+      <c r="H437" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I437" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="438" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C438" s="7" t="s">
+        <v>1986</v>
+      </c>
+      <c r="H438" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="I438" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="439" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C439" s="6" t="s">
+        <v>1987</v>
+      </c>
+      <c r="H439" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I439" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="440" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C440" s="7" t="s">
+        <v>1988</v>
+      </c>
+      <c r="H440" s="5" t="s">
+        <v>2001</v>
+      </c>
+      <c r="I440" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="441" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C441" s="6" t="s">
+        <v>1989</v>
+      </c>
+      <c r="H441" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I441" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="442" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C442" s="7" t="s">
+        <v>1990</v>
+      </c>
+      <c r="H442" s="5" t="s">
+        <v>2002</v>
+      </c>
+      <c r="I442" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="443" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C443" s="6" t="s">
+        <v>1991</v>
+      </c>
+      <c r="H443" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I443" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="444" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C444" s="7" t="s">
+        <v>1992</v>
+      </c>
+      <c r="H444" s="5" t="s">
+        <v>2001</v>
+      </c>
+      <c r="I444" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="445" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C445" s="6" t="s">
+        <v>1993</v>
+      </c>
+      <c r="H445" s="4" t="s">
+        <v>2005</v>
+      </c>
+      <c r="I445" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="446" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C446" s="7" t="s">
+        <v>1994</v>
+      </c>
+      <c r="H446" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I446" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="447" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C447" s="6" t="s">
+        <v>1995</v>
+      </c>
+      <c r="H447" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I447" s="6" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="448" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C448" s="7" t="s">
+        <v>1996</v>
+      </c>
+      <c r="H448" s="5" t="s">
+        <v>2001</v>
+      </c>
+      <c r="I448" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="449" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C449" s="6" t="s">
+        <v>1997</v>
+      </c>
+      <c r="H449" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I449" s="6">
+        <v>9433313918</v>
+      </c>
+    </row>
+    <row r="450" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C450" s="7" t="s">
+        <v>1998</v>
+      </c>
+      <c r="H450" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I450" s="7" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="451" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C451" s="6" t="s">
+        <v>1999</v>
+      </c>
+      <c r="H451" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I451" s="9" t="s">
+        <v>2000</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:K284" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
